--- a/samples/ss_kediri34_ingest.xlsx
+++ b/samples/ss_kediri34_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">

--- a/samples/ss_kediri34_ingest.xlsx
+++ b/samples/ss_kediri34_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 3,4 Kediri 500/150 kV</t>
+          <t>IBT 3 Kediri 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 3,4)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kediri (bus 150 kV)</t>
+          <t>IBT 4 Kediri 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 4 KDIRI7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>KDIRI7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>KDIRI5</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -791,12 +805,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLTU Pacitan (bus 150 kV)</t>
+          <t>Kediri (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PCTAN5</t>
+          <t>KDIRI5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -844,17 +858,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTU Pacitan</t>
+          <t>PLTU Pacitan (bus 150 kV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT_PCTAN</t>
+          <t>PCTAN5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -897,21 +911,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ngadi</t>
+          <t>PLTU Pacitan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NGTDI</t>
+          <t>KIT_PCTAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -950,12 +964,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pacitan</t>
+          <t>Ngadi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PCTAN</t>
+          <t>NGTDI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -986,14 +1000,10 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1007,12 +1017,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ponorogo (bus 150 kV)</t>
+          <t>Pacitan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PNRGO</t>
+          <t>PCTAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1021,7 +1031,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1043,10 +1053,14 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1060,12 +1074,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Suryazag</t>
+          <t>Ponorogo (bus 150 kV)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SYZAG</t>
+          <t>PNRGO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1096,14 +1110,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1117,12 +1127,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nganjuk (bus 150 kV)</t>
+          <t>Suryazag</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NGJUK5</t>
+          <t>SYZAG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1131,7 +1141,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1158,7 +1168,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>5;14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1174,12 +1184,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manisrejo (bus 150 kV)</t>
+          <t>Nganjuk (bus 150 kV)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MNRJO5</t>
+          <t>NGJUK5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1188,7 +1198,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1215,7 +1225,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5;14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1231,12 +1241,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ngawi</t>
+          <t>Manisrejo (bus 150 kV)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NGAWI</t>
+          <t>MNRJO5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1245,7 +1255,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1272,7 +1282,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1288,12 +1298,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sragen</t>
+          <t>Ngawi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SRGEN</t>
+          <t>NGAWI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1302,7 +1312,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1314,28 +1324,24 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>batas ke UP2B Jateng (SS Pedan 3,4)</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1349,12 +1355,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Banaran (bus 150 kV)</t>
+          <t>Sragen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNRAN5</t>
+          <t>SRGEN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1363,7 +1369,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1375,24 +1381,28 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>batas ke UP2B Jateng (SS Pedan 3,4)</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1406,12 +1416,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mojoagung</t>
+          <t>Banaran (bus 150 kV)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MJGNG</t>
+          <t>BNRAN5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1420,7 +1430,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1442,10 +1452,14 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1459,12 +1473,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sukorejo (bus 150 kV)</t>
+          <t>Mojoagung</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SKTIH5</t>
+          <t>MJGNG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1473,7 +1487,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1512,12 +1526,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kertosono (bus 150 kV)</t>
+          <t>Sukorejo (bus 150 kV)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KTSNO5</t>
+          <t>SKTIH5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1526,7 +1540,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1565,51 +1579,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Ponorogo</t>
+          <t>Kertosono (bus 150 kV)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IBT 1 PNRGO</t>
+          <t>KTSNO5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>PNRGO</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>PNRGO4</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV; beban 73%</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
@@ -1619,14 +1615,10 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1640,17 +1632,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ponorogo (bus 70 kV)</t>
+          <t>IBT 150/70 kV Ponorogo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PNRGO4</t>
+          <t>IBT 1 PNRGO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1658,15 +1650,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PNRGO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PNRGO4</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV; beban 73%</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -1676,10 +1686,14 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1693,12 +1707,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trenggalek</t>
+          <t>Ponorogo (bus 70 kV)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TGLEK</t>
+          <t>PNRGO4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1707,7 +1721,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1729,14 +1743,10 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1750,12 +1760,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tulungagung Pagerwojo</t>
+          <t>Trenggalek</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TLGPA</t>
+          <t>TGLEK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1764,7 +1774,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1791,7 +1801,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1807,12 +1817,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tlagong (seksi A)</t>
+          <t>Tulungagung Pagerwojo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TLGNGA</t>
+          <t>TLGPA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1821,7 +1831,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1833,11 +1843,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>seksi A</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
@@ -1847,10 +1853,14 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1864,21 +1874,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PLTA Tlagong</t>
+          <t>Tlagong (seksi A)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KIT_TLGNG</t>
+          <t>TLGNGA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1890,7 +1900,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>seksi A</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
@@ -1917,51 +1931,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBT 1,3 dan 2,6 Banaran 150/70 kV</t>
+          <t>PLTA Tlagong</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IBT 1 BNRAN5</t>
+          <t>KIT_TLGNG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>BNRAN5</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>BNRAN4</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>IBT 1,3 (44%) dan 2,6 (47%)</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -1971,14 +1967,10 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>7;8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1992,17 +1984,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Banaran (bus 70 kV)</t>
+          <t>IBT 1 dan 2,6 Banaran 150/70 kV</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BNRAN4</t>
+          <t>IBT 1 BNRAN5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2010,13 +2002,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>BNRAN5</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BNRAN4</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2028,10 +2034,14 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>7;8</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2045,37 +2055,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tlagong (seksi B)</t>
+          <t>IBT 3 dan 2,6 Banaran 150/70 kV</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TLGNGB</t>
+          <t>IBT 3 BNRAN5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>BNRAN5</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BNRAN4</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>seksi B</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
@@ -2085,10 +2105,14 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>7;8</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2102,12 +2126,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gudang Garam</t>
+          <t>Banaran (bus 70 kV)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GGRAM</t>
+          <t>BNRAN4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2116,7 +2140,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2155,12 +2179,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pare</t>
+          <t>Tlagong (seksi B)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PARE</t>
+          <t>TLGNGB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2183,7 +2207,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>single busbar</t>
+          <t>seksi B</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -2195,14 +2219,10 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>10;11</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2216,51 +2236,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IBT 1,3 dan 2 Manisrejo 150/70 kV</t>
+          <t>Gudang Garam</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IBT 1 MNRJO5</t>
+          <t>GGRAM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>MNRJO5</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>MNRJO4</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>IBT 1,3 dan 2</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
@@ -2270,14 +2272,10 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2291,12 +2289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Manisrejo (bus 70 kV)</t>
+          <t>Pare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MNRJO4</t>
+          <t>PARE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2305,7 +2303,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2317,7 +2315,11 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>single busbar</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
@@ -2327,10 +2329,14 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>10;11</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2344,31 +2350,45 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mergen</t>
+          <t>IBT 1 dan 2 Manisrejo 150/70 kV</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MRGEN</t>
+          <t>IBT 1 MNRJO5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MNRJO5</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MNRJO4</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2385,7 +2405,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2401,31 +2421,45 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Magetan</t>
+          <t>IBT 3 dan 2 Manisrejo 150/70 kV</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MGTAN</t>
+          <t>IBT 3 MNRJO5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>MNRJO5</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MNRJO4</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2442,7 +2476,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2458,12 +2492,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dolopo</t>
+          <t>Manisrejo (bus 70 kV)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DLOPO</t>
+          <t>MNRJO4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2472,7 +2506,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2494,20 +2528,187 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mergen</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MRGEN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Magetan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MGTAN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dolopo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DLOPO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4171,12 +4372,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV PLTU Pacitan- New Pacitan dan SUTT 150 kV GI New Pacitan-Ponorogo sudah melebihi nilai SIL jika 2 unit PLTU Pacitan operasi maksimum memasok ke arah Jawa Timur</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV PLTU Pacitan- New Pacitan dan SUTT 150 kV GI New Pacitan-Ponorogo sudah melebihi nilai SIL jika 2 unit PLTU Pacitan operasi maksimum memasok ke arah Jawa Timur</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4241,12 +4442,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] GI 150 kV Surya Zig- zag hanya single Busbar</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV Surya Zig- zag hanya single Busbar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4276,12 +4477,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] PHT150 kVBanaran- Surya zigzag-Nganjuk II - Manisrejoterjadi derating700 A dikarenakan ada penurunan andongan di ruas tersebut</t>
+          <t>[BELUM_DITETAPKAN] PHT150 kVBanaran- Surya zigzag-Nganjuk II - Manisrejoterjadi derating700 A dikarenakan ada penurunan andongan di ruas tersebut</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4311,12 +4512,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] IBT 150/70 kV, 100 MVA di GI Ponorogo sudah berbeban &gt;93% dengan jumlah IBT hanya 1, sehingga apabila terjadi gangguan pada IBT tersebut maka akan terjadi pemadaman dan sulit untuk melakukan pemeliharaan</t>
+          <t>[BELUM_DITETAPKAN] IBT 150/70 kV, 100 MVA di GI Ponorogo sudah berbeban &gt;93% dengan jumlah IBT hanya 1, sehingga apabila terjadi gangguan pada IBT tersebut maka akan terjadi pemadaman dan sulit untuk melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4451,12 +4652,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV Pare hanya singleBusbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Pare hanya singleBusbar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4486,12 +4687,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV PLTA Tulungagung dan GI 70 kV Dolopo hanya single Busbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV PLTA Tulungagung dan GI 70 kV Dolopo hanya single Busbar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4521,12 +4722,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1] Kapasitas IBT 150/70 kV Manisrejo tidak sama (IBT-1: 100 MVA, IBT-2: 35 MVA, IBT-3: 100 MVA).Akan terjadi overload pada IBT 2 35 MVA apabila terjadi kontingensi N-1-1 pada IBT dengan kapasitas 100 MVA</t>
+          <t>[N-1-1] Kapasitas IBT 150/70 kV Manisrejo tidak sama (IBT-1: 100 MVA, IBT-2: 35 MVA, IBT-3: 100 MVA).Akan terjadi overload pada IBT 2 35 MVA apabila terjadi kontingensi N-1-1 pada IBT dengan kapasitas 100 MVA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4626,12 +4827,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi Drop tegangan di Subsistem Kediri 3,4 pada GI 150 kV Ngawi, GI 150 kV New Nganjuk dan GI 150 kV Ponorogo</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di Subsistem Kediri 3,4 pada GI 150 kV Ngawi, GI 150 kV New Nganjuk dan GI 150 kV Ponorogo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
